--- a/naver-place-crawler/results_health/의정부_헬스장.xlsx
+++ b/naver-place-crawler/results_health/의정부_헬스장.xlsx
@@ -718,10 +718,10 @@
         <v>175</v>
       </c>
       <c r="Q3" t="n">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="R3" t="n">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -747,39 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>피트니스플레이스 헬스&amp;PT 장암점</t>
+          <t>바디붐휘트니스 민락점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fitnessplace5@naver.com</t>
+          <t>bodyboom_pt@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1414-9679</t>
+          <t>031-851-3456</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 의정부시 회룡로 188 장암골드프라자 지하2층</t>
+          <t>경기도 의정부시 오목로225번길 140 성산타워7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xmxkhTG</t>
+          <t>https://www.instagram.com/piece_gym_031_480_6565</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -800,7 +800,7 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>1160</v>
+      </c>
+      <c r="Q4" t="n">
         <v>732</v>
       </c>
-      <c r="Q4" t="n">
-        <v>191</v>
-      </c>
       <c r="R4" t="n">
-        <v>923</v>
+        <v>1892</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1658324530</t>
+          <t>36680429</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1658324530</t>
+          <t>https://m.place.naver.com/place/36680429</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -846,34 +846,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>희핏 PT&amp;헬스</t>
+          <t>피트니스플레이스 헬스&amp;PT 장암점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>heegym@naver.com</t>
+          <t>fitnessplace5@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1459-0281</t>
+          <t>0507-1414-9679</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 432 지하1층</t>
+          <t>경기도 의정부시 회룡로 188 장암골드프라자 지하2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/heegym</t>
+          <t>https://pf.kakao.com/_xmxkhTG</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -894,7 +894,7 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>188</v>
+        <v>732</v>
       </c>
       <c r="Q5" t="n">
-        <v>449</v>
+        <v>191</v>
       </c>
       <c r="R5" t="n">
-        <v>637</v>
+        <v>923</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1135733595</t>
+          <t>1658324530</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135733595</t>
+          <t>https://m.place.naver.com/place/1658324530</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1029,34 +1029,34 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>바디붐휘트니스 민락점</t>
+          <t>스포애니 의정부역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodyboom_pt@naver.com</t>
+          <t>spoany_62@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>031-851-3456</t>
+          <t>0507-1409-9618</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 의정부시 오목로225번길 140 성산타워7층</t>
+          <t>경기도 의정부시 평화로 540 9, 10 층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/piece_gym_031_480_6565</t>
+          <t>https://blog.naver.com/spoany_62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1160</v>
+        <v>2016</v>
       </c>
       <c r="Q7" t="n">
-        <v>732</v>
+        <v>1950</v>
       </c>
       <c r="R7" t="n">
-        <v>1892</v>
+        <v>3966</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>36680429</t>
+          <t>1886274354</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36680429</t>
+          <t>https://m.place.naver.com/place/1886274354</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>스포애니 의정부역점</t>
+          <t>아테나휘트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>spoany_62@naver.com</t>
+          <t>athenagym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1409-9618</t>
+          <t>0507-1334-7642</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 540 9, 10 층</t>
+          <t>경기도 의정부시 시민로121번길 28 지하1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_62</t>
+          <t>https://blog.naver.com/athenagym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2015</v>
+        <v>2898</v>
       </c>
       <c r="Q8" t="n">
-        <v>1949</v>
+        <v>964</v>
       </c>
       <c r="R8" t="n">
-        <v>3964</v>
+        <v>3862</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1886274354</t>
+          <t>1788806049</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886274354</t>
+          <t>https://m.place.naver.com/place/1788806049</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1222,29 +1222,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>아테나휘트니스</t>
+          <t>올인짐 의정부본점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>athenagym@naver.com</t>
+          <t>brakofficial@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1334-7642</t>
+          <t>0507-1397-4344</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 의정부시 시민로121번길 28 지하1층</t>
+          <t>경기도 의정부시 충의로 25 5층 501~508호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/athenagym</t>
+          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2897</v>
+        <v>769</v>
       </c>
       <c r="Q9" t="n">
-        <v>964</v>
+        <v>250</v>
       </c>
       <c r="R9" t="n">
-        <v>3861</v>
+        <v>1019</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1788806049</t>
+          <t>2023029424</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1788806049</t>
+          <t>https://m.place.naver.com/place/2023029424</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>올인짐 의정부본점</t>
+          <t>꿀핏휘트니스 신곡점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>brakofficial@naver.com</t>
+          <t>honeyfit_3@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1397-4344</t>
+          <t>0507-1434-2439</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 의정부시 충의로 25 5층 501~508호</t>
+          <t>경기도 의정부시 추동로 15 대명프라자 6층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
+          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>765</v>
+        <v>131</v>
       </c>
       <c r="Q10" t="n">
-        <v>250</v>
+        <v>582</v>
       </c>
       <c r="R10" t="n">
-        <v>1015</v>
+        <v>713</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2023029424</t>
+          <t>2070790169</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023029424</t>
+          <t>https://m.place.naver.com/place/2070790169</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1410,29 +1410,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>꿀핏휘트니스 신곡점</t>
+          <t>fitness H</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>honeyfit_3@naver.com</t>
+          <t>armoxic@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1434-2439</t>
+          <t>0507-1382-6733</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 의정부시 추동로 15 대명프라자 6층</t>
+          <t>경기도 의정부시 평화로 170 동인빌딩 6,7,8층 fitness H</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
+          <t>https://blog.naver.com/armoxic</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="Q11" t="n">
-        <v>572</v>
+        <v>837</v>
       </c>
       <c r="R11" t="n">
-        <v>703</v>
+        <v>952</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2070790169</t>
+          <t>12990269</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2070790169</t>
+          <t>https://m.place.naver.com/place/12990269</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1504,29 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fitness H</t>
+          <t>얼리버드짐</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>armoxic@naver.com</t>
+          <t>earlybirdgym@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1382-6733</t>
+          <t>0507-1301-1421</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 170 동인빌딩 6,7,8층 fitness H</t>
+          <t>경기도 의정부시 발곡로 22 신풍프라자 B1층 전체</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/armoxic</t>
+          <t>https://blog.naver.com/earlybirdgym</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>115</v>
+        <v>1549</v>
       </c>
       <c r="Q12" t="n">
-        <v>837</v>
+        <v>894</v>
       </c>
       <c r="R12" t="n">
-        <v>952</v>
+        <v>2443</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>12990269</t>
+          <t>1921522541</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12990269</t>
+          <t>https://m.place.naver.com/place/1921522541</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1598,29 +1598,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>얼리버드짐</t>
+          <t>의정부짐</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>earlybirdgym@naver.com</t>
+          <t>dmlwjdqnwla1@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1301-1421</t>
+          <t>0507-1386-8583</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 의정부시 발곡로 22 신풍프라자 B1층 전체</t>
+          <t>경기도 의정부시 경의로 108 한양수자인파크뷰 B101호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/earlybirdgym</t>
+          <t>https://blog.naver.com/dmlwjdqnwla1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1655,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1547</v>
+        <v>1014</v>
       </c>
       <c r="Q13" t="n">
-        <v>891</v>
+        <v>663</v>
       </c>
       <c r="R13" t="n">
-        <v>2438</v>
+        <v>1677</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,12 +1670,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1921522541</t>
+          <t>1267068271</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1921522541</t>
+          <t>https://m.place.naver.com/place/1267068271</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1692,29 +1692,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>의정부짐</t>
+          <t>밀리언짐 회룡점</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dmlwjdqnwla1@naver.com</t>
+          <t>milliongym2@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1386-8583</t>
+          <t>0507-1413-1542</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>경기도 의정부시 경의로 108 한양수자인파크뷰 B101호</t>
+          <t>경기도 의정부시 평화로 359 지하1층</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dmlwjdqnwla1</t>
+          <t>https://blog.naver.com/milliongym2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1749,13 +1749,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1014</v>
+        <v>3380</v>
       </c>
       <c r="Q14" t="n">
-        <v>663</v>
+        <v>942</v>
       </c>
       <c r="R14" t="n">
-        <v>1677</v>
+        <v>4322</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1764,12 +1764,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1267068271</t>
+          <t>1262703425</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267068271</t>
+          <t>https://m.place.naver.com/place/1262703425</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1846,10 +1846,10 @@
         <v>1078</v>
       </c>
       <c r="Q15" t="n">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="R15" t="n">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1880,29 +1880,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>밀리언짐 회룡점</t>
+          <t>벙커짐</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>milliongym2@naver.com</t>
+          <t>bunkergym_@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1413-1542</t>
+          <t>0507-1397-1069</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 359 지하1층</t>
+          <t>경기도 의정부시 발곡로 26 B1층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/milliongym2</t>
+          <t>https://blog.naver.com/bunkergym_</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3380</v>
+        <v>1738</v>
       </c>
       <c r="Q16" t="n">
-        <v>942</v>
+        <v>1087</v>
       </c>
       <c r="R16" t="n">
-        <v>4322</v>
+        <v>2825</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1952,12 +1952,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1262703425</t>
+          <t>1880851837</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1262703425</t>
+          <t>https://m.place.naver.com/place/1880851837</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1974,29 +1974,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>벙커짐</t>
+          <t>F45 의정부</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bunkergym_@naver.com</t>
+          <t>f45_uijeongbu@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1397-1069</t>
+          <t>0507-1351-0357</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>경기도 의정부시 발곡로 26 B1층</t>
+          <t>경기도 의정부시 평화로 457 송헌빌딩 5층</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bunkergym_</t>
+          <t>https://www.instagram.com/f45_uijeongbu</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1737</v>
+        <v>109</v>
       </c>
       <c r="Q17" t="n">
-        <v>1087</v>
+        <v>131</v>
       </c>
       <c r="R17" t="n">
-        <v>2824</v>
+        <v>240</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1880851837</t>
+          <t>1734901599</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1880851837</t>
+          <t>https://m.place.naver.com/place/1734901599</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2162,29 +2162,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>F45 의정부</t>
+          <t>삼성휘트니스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>f45_uijeongbu@naver.com</t>
+          <t>samsung_fit@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1351-0357</t>
+          <t>031-836-9772</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 457 송헌빌딩 5층</t>
+          <t>경기도 의정부시 신곡로 47 우신프라자 5층</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/f45_uijeongbu</t>
+          <t>https://www.instagram.com/samsung_fitness_/</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2210,7 +2210,7 @@
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2219,13 +2219,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="Q19" t="n">
-        <v>130</v>
+        <v>326</v>
       </c>
       <c r="R19" t="n">
-        <v>239</v>
+        <v>434</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1734901599</t>
+          <t>19578878</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1734901599</t>
+          <t>https://m.place.naver.com/place/19578878</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2256,29 +2256,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>삼성휘트니스</t>
+          <t>지엘핏 가능점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>samsung_fit@naver.com</t>
+          <t>zielfit2@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>031-836-9772</t>
+          <t>0507-1406-9244</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>경기도 의정부시 신곡로 47 우신프라자 5층</t>
+          <t>경기도 의정부시 신촌로29번길 24 3층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/samsung_fitness_/</t>
+          <t>https://blog.naver.com/zielfit2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2304,7 +2304,7 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>108</v>
+        <v>540</v>
       </c>
       <c r="Q20" t="n">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="R20" t="n">
-        <v>421</v>
+        <v>894</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>19578878</t>
+          <t>1335830135</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/19578878</t>
+          <t>https://m.place.naver.com/place/1335830135</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2350,29 +2350,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>바디피트니스</t>
+          <t>파무짐트레이닝</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bodyfitness_u@naver.com</t>
+          <t>kimdal93@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1422-4013</t>
+          <t>0507-1404-9906</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>경기도 의정부시 청사로47번길 15 골드피아 506호</t>
+          <t>경기도 의정부시 신흥로258번길 35 뷰레지던스 지하1층 파무짐</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyfitness_u</t>
+          <t>https://blog.naver.com/kimdal93</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2407,13 +2407,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="Q21" t="n">
-        <v>648</v>
+        <v>437</v>
       </c>
       <c r="R21" t="n">
-        <v>769</v>
+        <v>510</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1166236352</t>
+          <t>1505018776</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1166236352</t>
+          <t>https://m.place.naver.com/place/1505018776</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">

--- a/naver-place-crawler/results_health/의정부_헬스장.xlsx
+++ b/naver-place-crawler/results_health/의정부_헬스장.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>해머하우스 회룡점 헬스&amp;PT</t>
+          <t>포레스포 헬스PT 골프 필라테스 클라이밍</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hammer_house_2@naver.com</t>
+          <t>incar50@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1356-0176</t>
+          <t>0507-1365-6211</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 389 지하1층</t>
+          <t>경기 의정부시 청사로47번길 18 로얄프라자 6층 601~603호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hammer_house_2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,20 +596,24 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ybhi</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>354</v>
+        <v>575</v>
       </c>
       <c r="Q2" t="n">
-        <v>344</v>
+        <v>276</v>
       </c>
       <c r="R2" t="n">
-        <v>698</v>
+        <v>851</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1470344233</t>
+          <t>1258663714</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1470344233</t>
+          <t>https://m.place.naver.com/place/1258663714</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>여성전용 하이핏 의정부 헬스장</t>
+          <t>스포애니 의정부역점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>highfit031@naver.com</t>
+          <t>spoany_62@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1424-2285</t>
+          <t>0507-1409-9618</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 의정부시 신흥로 193 동일빌딩 4층</t>
+          <t>경기 의정부시 평화로 540 9, 10 층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/highfit02</t>
+          <t>https://blog.naver.com/spoany_62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4fckh</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>175</v>
+        <v>2032</v>
       </c>
       <c r="Q3" t="n">
-        <v>520</v>
+        <v>1978</v>
       </c>
       <c r="R3" t="n">
-        <v>695</v>
+        <v>4010</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1877908337</t>
+          <t>1886274354</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877908337</t>
+          <t>https://m.place.naver.com/place/1886274354</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>바디붐휘트니스 민락점 헬스&amp;PT</t>
+          <t>올인짐 의정부본점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bodyboom_pt@naver.com</t>
+          <t>brakofficial@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>031-851-3456</t>
+          <t>0507-1397-4344</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 의정부시 오목로225번길 140 성산타워7층</t>
+          <t>경기 의정부시 충의로 25 5층 501~508호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/piece_gym_031_480_6565</t>
+          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wbijmqx</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1160</v>
+        <v>779</v>
       </c>
       <c r="Q4" t="n">
-        <v>732</v>
+        <v>245</v>
       </c>
       <c r="R4" t="n">
-        <v>1892</v>
+        <v>1024</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +836,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36680429</t>
+          <t>2023029424</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36680429</t>
+          <t>https://m.place.naver.com/place/2023029424</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>피트니스플레이스 헬스&amp;PT 장암점</t>
+          <t>꿀핏휘트니스 신곡점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fitnessplace5@naver.com</t>
+          <t>honeyfit_3@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1414-9679</t>
+          <t>0507-1434-2439</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 의정부시 회룡로 188 장암골드프라자 지하2층</t>
+          <t>경기 의정부시 추동로 15 대명프라자 6층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xmxkhTG</t>
+          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -888,13 +900,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wyh5tgc</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>732</v>
+        <v>142</v>
       </c>
       <c r="Q5" t="n">
-        <v>191</v>
+        <v>630</v>
       </c>
       <c r="R5" t="n">
-        <v>923</v>
+        <v>772</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,51 +934,51 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1658324530</t>
+          <t>2070790169</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1658324530</t>
+          <t>https://m.place.naver.com/place/2070790169</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>휴먼 근골격 운동센터 의정부 PT 민락점</t>
+          <t>아테나휘트니스</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hue_musculoskeleta@naver.com</t>
+          <t>athenagym@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1456-0358</t>
+          <t>0507-1334-7642</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 의정부시 오목로205번길 21 골든프라자3차 4층 404-1호</t>
+          <t>경기 의정부시 시민로121번길 28 지하1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hue_musculoskeleta</t>
+          <t>https://blog.naver.com/athenagym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5z8kw</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>358</v>
+        <v>2910</v>
       </c>
       <c r="Q6" t="n">
-        <v>1490</v>
+        <v>967</v>
       </c>
       <c r="R6" t="n">
-        <v>1848</v>
+        <v>3877</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1045318033</t>
+          <t>1788806049</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1045318033</t>
+          <t>https://m.place.naver.com/place/1788806049</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>스포애니 의정부역점</t>
+          <t>바디붐휘트니스 의정부역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>spoany_62@naver.com</t>
+          <t>bodyboomone@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1409-9618</t>
+          <t>0507-1408-9680</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 540 9, 10 층</t>
+          <t>경기 의정부시 태평로99번길 17 베스트프라자 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_62</t>
+          <t>https://blog.naver.com/bodyboomone</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1076,10 +1096,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vdzl</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2016</v>
+        <v>1092</v>
       </c>
       <c r="Q7" t="n">
-        <v>1950</v>
+        <v>609</v>
       </c>
       <c r="R7" t="n">
-        <v>3966</v>
+        <v>1701</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,61 +1130,61 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1886274354</t>
+          <t>21598453</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1886274354</t>
+          <t>https://m.place.naver.com/place/21598453</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아테나휘트니스</t>
+          <t>메이드라인 다이어트 의정부점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>athenagym@naver.com</t>
+          <t>made-line@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1334-7642</t>
+          <t>0507-1304-3854</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 의정부시 시민로121번길 28 지하1층</t>
+          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/athenagym</t>
+          <t>https://made-line.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4poji</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2898</v>
+        <v>668</v>
       </c>
       <c r="Q8" t="n">
-        <v>964</v>
+        <v>286</v>
       </c>
       <c r="R8" t="n">
-        <v>3862</v>
+        <v>954</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1788806049</t>
+          <t>1572526028</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1788806049</t>
+          <t>https://m.place.naver.com/place/1572526028</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>올인짐 의정부본점</t>
+          <t>캥거루복싱GYM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>brakofficial@naver.com</t>
+          <t>boxing6989@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1397-4344</t>
+          <t>031-853-6989</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 의정부시 충의로 25 5층 501~508호</t>
+          <t>경기 의정부시 오목로205번길 29 5층 501,502호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1254,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1264,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wmk4z6o</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>769</v>
+        <v>173</v>
       </c>
       <c r="Q9" t="n">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="R9" t="n">
-        <v>1019</v>
+        <v>435</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2023029424</t>
+          <t>37373427</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023029424</t>
+          <t>https://m.place.naver.com/place/37373427</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1348,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>꿀핏휘트니스 신곡점</t>
+          <t>OPT트레이닝센터 다이어트 피지컬 1:1PT 금오점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>honeyfit_3@naver.com</t>
+          <t>sunnydue@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1434-2439</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 의정부시 추동로 15 대명프라자 6층</t>
+          <t>경기 의정부시 청사로 45 플래티넘1프라자 701호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
+          <t>https://www.instagram.com/opt087</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,10 +1386,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45dto</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1373,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>582</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>713</v>
+        <v>12</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2070790169</t>
+          <t>1913501005</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2070790169</t>
+          <t>https://m.place.naver.com/place/1913501005</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1410,34 +1442,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fitness H</t>
+          <t>한번더재활운동센터</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>armoxic@naver.com</t>
+          <t>kongja21@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1382-6733</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 의정부시 평화로 170 동인빌딩 6,7,8층 fitness H</t>
+          <t>경기 의정부시 세석로 20 2층 204호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/armoxic</t>
+          <t>https://youtube.com/@한번더재활운동센터</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,15 +1475,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/weppdix</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="Q11" t="n">
-        <v>837</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>952</v>
+        <v>67</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,51 +1514,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>12990269</t>
+          <t>2072368822</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/12990269</t>
+          <t>https://m.place.naver.com/place/2072368822</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내골프연습장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>얼리버드짐</t>
+          <t>GDR골프아카데미 고산지구점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>earlybirdgym@naver.com</t>
+          <t>gdrgs0753@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1301-1421</t>
+          <t>0507-1471-0754</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 의정부시 발곡로 22 신풍프라자 B1층 전체</t>
+          <t>경기 의정부시 월유로 16 GS프라자 9층 903호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/earlybirdgym</t>
+          <t>https://blog.naver.com/gdrgs0753</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1546,10 +1578,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4539d</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1549</v>
+        <v>648</v>
       </c>
       <c r="Q12" t="n">
-        <v>894</v>
+        <v>459</v>
       </c>
       <c r="R12" t="n">
-        <v>2443</v>
+        <v>1107</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,863 +1612,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1921522541</t>
+          <t>1057272528</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1921522541</t>
+          <t>https://m.place.naver.com/place/1057272528</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>의정부짐</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>dmlwjdqnwla1@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1386-8583</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 의정부시 경의로 108 한양수자인파크뷰 B101호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/dmlwjdqnwla1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>1014</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>663</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1677</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1267068271</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1267068271</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>밀리언짐 회룡점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>milliongym2@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1413-1542</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 의정부시 평화로 359 지하1층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/milliongym2</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>3380</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>942</v>
-      </c>
-      <c r="R14" t="n">
-        <v>4322</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1262703425</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1262703425</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>바디붐휘트니스 의정부역점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>bodyboomone@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1408-9680</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경기도 의정부시 태평로99번길 17 베스트프라자 3층</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bodyboomone</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>1078</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>606</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1684</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>21598453</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/21598453</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>벙커짐</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>bunkergym_@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1397-1069</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경기도 의정부시 발곡로 26 B1층</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/bunkergym_</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>1738</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1087</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2825</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1880851837</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1880851837</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>F45 의정부</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>f45_uijeongbu@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1351-0357</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경기도 의정부시 평화로 457 송헌빌딩 5층</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/f45_uijeongbu</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>109</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>131</v>
-      </c>
-      <c r="R17" t="n">
-        <v>240</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1734901599</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1734901599</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>오픈짐 의정부민락점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>choisehwan80@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1391-0969</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경기도 의정부시 오목로 207 정원빌딩 2층</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/choisehwan80/224210429320</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>263</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>328</v>
-      </c>
-      <c r="R18" t="n">
-        <v>591</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1702970976</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1702970976</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>삼성휘트니스</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>samsung_fit@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>031-836-9772</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경기도 의정부시 신곡로 47 우신프라자 5층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/samsung_fitness_/</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>108</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>326</v>
-      </c>
-      <c r="R19" t="n">
-        <v>434</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>19578878</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/19578878</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>지엘핏 가능점</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>zielfit2@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1406-9244</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경기도 의정부시 신촌로29번길 24 3층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/zielfit2</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>540</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>354</v>
-      </c>
-      <c r="R20" t="n">
-        <v>894</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1335830135</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1335830135</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>파무짐트레이닝</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>kimdal93@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1404-9906</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경기도 의정부시 신흥로258번길 35 뷰레지던스 지하1층 파무짐</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/kimdal93</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>73</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>437</v>
-      </c>
-      <c r="R21" t="n">
-        <v>510</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1505018776</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1505018776</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/의정부_헬스장.xlsx
+++ b/naver-place-crawler/results_health/의정부_헬스장.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="Q2" t="n">
         <v>276</v>
       </c>
       <c r="R2" t="n">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_62</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="Q3" t="n">
-        <v>1978</v>
+        <v>1983</v>
       </c>
       <c r="R3" t="n">
-        <v>4010</v>
+        <v>4021</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -824,10 +824,10 @@
         <v>779</v>
       </c>
       <c r="Q4" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="R4" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -880,17 +880,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="Q5" t="n">
-        <v>630</v>
+        <v>640</v>
       </c>
       <c r="R5" t="n">
-        <v>772</v>
+        <v>788</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/athenagym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2910</v>
+        <v>2915</v>
       </c>
       <c r="Q6" t="n">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="R6" t="n">
-        <v>3877</v>
+        <v>3883</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodyboomone@naver.com</t>
+          <t>bodyboom_ujb@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyboomone</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="Q7" t="n">
         <v>609</v>
       </c>
       <c r="R7" t="n">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q9" t="n">
         <v>262</v>
       </c>
       <c r="R9" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OPT트레이닝센터 다이어트 피지컬 1:1PT 금오점</t>
+          <t>한번더재활운동센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sunnydue@naver.com</t>
+          <t>kongja21@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1361,12 +1361,12 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 청사로 45 플래티넘1프라자 701호</t>
+          <t>경기 의정부시 세석로 20 2층 204호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/opt087</t>
+          <t>https://youtube.com/@한번더재활운동센터</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45dto</t>
+          <t>https://talk.naver.com/ct/weppdix</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>12</v>
+        <v>67</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,57 +1420,61 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1913501005</t>
+          <t>2072368822</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1913501005</t>
+          <t>https://m.place.naver.com/place/2072368822</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내골프연습장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한번더재활운동센터</t>
+          <t>GDR골프아카데미 고산지구점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>kongja21@naver.com</t>
+          <t>gdrgs0753@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1471-0754</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 세석로 20 2층 204호</t>
+          <t>경기 의정부시 월유로 16 GS프라자 9층 903호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://youtube.com/@한번더재활운동센터</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/weppdix</t>
+          <t>https://talk.naver.com/ct/w4539d</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1495,17 +1499,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>65</v>
+        <v>648</v>
       </c>
       <c r="Q11" t="n">
-        <v>2</v>
+        <v>459</v>
       </c>
       <c r="R11" t="n">
-        <v>67</v>
+        <v>1107</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,51 +1518,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2072368822</t>
+          <t>1057272528</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072368822</t>
+          <t>https://m.place.naver.com/place/1057272528</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>실내골프연습장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GDR골프아카데미 고산지구점</t>
+          <t>필라테스 림 탑석역 점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>gdrgs0753@naver.com</t>
+          <t>pilateslim201@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1471-0754</t>
+          <t>0507-1440-2832</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 의정부시 월유로 16 GS프라자 9층 903호</t>
+          <t>경기 의정부시 오목로 33 2층 201호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gdrgs0753</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1568,12 +1572,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1583,12 +1587,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4539d</t>
+          <t>https://talk.naver.com/ct/wjnmgc7</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1597,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>648</v>
+        <v>711</v>
       </c>
       <c r="Q12" t="n">
-        <v>459</v>
+        <v>1091</v>
       </c>
       <c r="R12" t="n">
-        <v>1107</v>
+        <v>1802</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1057272528</t>
+          <t>1347002622</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057272528</t>
+          <t>https://m.place.naver.com/place/1347002622</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/의정부_헬스장.xlsx
+++ b/naver-place-crawler/results_health/의정부_헬스장.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/incar50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany_62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -922,10 +922,10 @@
         <v>148</v>
       </c>
       <c r="Q5" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="R5" t="n">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/athenagym</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodyboom_ujb@naver.com</t>
+          <t>bodyboomone@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bodyboomone</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1147,39 +1147,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>메이드라인 다이어트 의정부점</t>
+          <t>핏걸 민락점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>made-line@naver.com</t>
+          <t>flffltpqms@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1304-3854</t>
+          <t>031-851-3367</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
+          <t>경기 의정부시 오목로225번길 157 폴리프라자3 301호 핏걸</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://made-line.co.kr</t>
+          <t>http://www.fitgirl.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,19 +1189,15 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4poji</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1209,17 +1205,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>668</v>
+        <v>159</v>
       </c>
       <c r="Q8" t="n">
-        <v>286</v>
+        <v>210</v>
       </c>
       <c r="R8" t="n">
-        <v>954</v>
+        <v>369</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1572526028</t>
+          <t>79195868</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572526028</t>
+          <t>https://m.place.naver.com/place/79195868</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>캥거루복싱GYM</t>
+          <t>희핏 PT&amp;헬스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>boxing6989@naver.com</t>
+          <t>heegym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-853-6989</t>
+          <t>0507-1459-0281</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 29 5층 501,502호</t>
+          <t>경기 의정부시 평화로 432 지하1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/heegym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1282,12 +1278,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmk4z6o</t>
+          <t>https://talk.naver.com/ct/w4e8qf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="Q9" t="n">
-        <v>262</v>
+        <v>455</v>
       </c>
       <c r="R9" t="n">
-        <v>436</v>
+        <v>643</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37373427</t>
+          <t>1135733595</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37373427</t>
+          <t>https://m.place.naver.com/place/1135733595</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,35 +1339,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>한번더재활운동센터</t>
+          <t>메이드라인 다이어트 의정부점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>kongja21@naver.com</t>
+          <t>madeline-@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1304-3854</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 세석로 20 2층 204호</t>
+          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://youtube.com/@한번더재활운동센터</t>
+          <t>https://made-line.co.kr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/weppdix</t>
+          <t>https://talk.naver.com/ct/w4poji</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>65</v>
+        <v>668</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>286</v>
       </c>
       <c r="R10" t="n">
-        <v>67</v>
+        <v>954</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2072368822</t>
+          <t>1572526028</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072368822</t>
+          <t>https://m.place.naver.com/place/1572526028</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>실내골프연습장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GDR골프아카데미 고산지구점</t>
+          <t>캥거루복싱GYM</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>gdrgs0753@naver.com</t>
+          <t>boxing6989@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1471-0754</t>
+          <t>031-853-6989</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 월유로 16 GS프라자 9층 903호</t>
+          <t>경기 의정부시 오목로205번길 29 5층 501,502호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kangaroo__boxinggym</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4539d</t>
+          <t>https://talk.naver.com/ct/wmk4z6o</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>648</v>
+        <v>174</v>
       </c>
       <c r="Q11" t="n">
-        <v>459</v>
+        <v>262</v>
       </c>
       <c r="R11" t="n">
-        <v>1107</v>
+        <v>436</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1057272528</t>
+          <t>37373427</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1057272528</t>
+          <t>https://m.place.naver.com/place/37373427</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1535,96 +1535,288 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>필라테스 림 탑석역 점</t>
+          <t>한번더재활운동센터</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pilateslim201@naver.com</t>
+          <t>kongja21@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1440-2832</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
+          <t>경기 의정부시 세석로 20 2층 204호</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://youtube.com/@한번더재활운동센터</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/weppdix</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>65</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
+        <v>67</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>2072368822</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2072368822</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>실내골프연습장</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GDR골프아카데미 고산지구점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gdrgs0753@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1471-0754</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>경기 의정부시 월유로 16 GS프라자 9층 903호</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/gdrgs0753</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4539d</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>648</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>459</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1107</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1057272528</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057272528</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>필라테스 림 탑석역 점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pilateslim201@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1440-2832</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>경기 의정부시 오목로 33 2층 201호</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pilateslim201/224254625203</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/wjnmgc7</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
         <v>711</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q14" t="n">
         <v>1091</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R14" t="n">
         <v>1802</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
         <is>
           <t>1347002622</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1347002622</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/의정부_헬스장.xlsx
+++ b/naver-place-crawler/results_health/의정부_헬스장.xlsx
@@ -421,13 +421,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/incar50</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -628,10 +628,10 @@
         <v>577</v>
       </c>
       <c r="Q2" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="R2" t="n">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_62</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -726,10 +726,10 @@
         <v>2042</v>
       </c>
       <c r="Q3" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="R3" t="n">
-        <v>4033</v>
+        <v>4032</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2919</v>
+        <v>2920</v>
       </c>
       <c r="Q5" t="n">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="R5" t="n">
-        <v>3887</v>
+        <v>3889</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1020,10 +1020,10 @@
         <v>154</v>
       </c>
       <c r="Q6" t="n">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="R6" t="n">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1147,39 +1147,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>핏걸 민락점</t>
+          <t>메이드라인 다이어트 의정부점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>flffltpqms@naver.com</t>
+          <t>madeline-@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>031-851-3367</t>
+          <t>0507-1304-3854</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로225번길 157 폴리프라자3 301호 핏걸</t>
+          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>http://www.fitgirl.kr</t>
+          <t>https://made-line.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1189,15 +1189,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4poji</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,17 +1209,17 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>159</v>
+        <v>668</v>
       </c>
       <c r="Q8" t="n">
-        <v>210</v>
+        <v>287</v>
       </c>
       <c r="R8" t="n">
-        <v>369</v>
+        <v>955</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>79195868</t>
+          <t>1572526028</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/79195868</t>
+          <t>https://m.place.naver.com/place/1572526028</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1241,29 +1245,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>희핏 PT&amp;헬스</t>
+          <t>캥거루복싱GYM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>heegym@naver.com</t>
+          <t>boxing6989@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1459-0281</t>
+          <t>031-853-6989</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 의정부시 평화로 432 지하1층</t>
+          <t>경기 의정부시 오목로205번길 29 5층 501,502호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4e8qf</t>
+          <t>https://talk.naver.com/ct/wmk4z6o</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="Q9" t="n">
-        <v>456</v>
+        <v>262</v>
       </c>
       <c r="R9" t="n">
-        <v>644</v>
+        <v>436</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1135733595</t>
+          <t>37373427</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1135733595</t>
+          <t>https://m.place.naver.com/place/37373427</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1339,49 +1343,45 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>메이드라인 다이어트 의정부점</t>
+          <t>OPT트레이닝센터 다이어트 피지컬 1:1PT 금오점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>madeline-@naver.com</t>
+          <t>sunnydue@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1304-3854</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
+          <t>경기 의정부시 청사로 45 플래티넘1프라자 701호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://made-line.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4poji</t>
+          <t>https://talk.naver.com/ct/w45dto</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>668</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
-        <v>286</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>954</v>
+        <v>12</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1572526028</t>
+          <t>1913501005</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572526028</t>
+          <t>https://m.place.naver.com/place/1913501005</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>캥거루복싱GYM</t>
+          <t>LT짐 PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>boxing6989@naver.com</t>
+          <t>ph5734@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>031-853-6989</t>
+          <t>0507-1397-5346</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 29 5층 501,502호</t>
+          <t>경기 의정부시 경의로 57 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kangaroo__boxinggym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmk4z6o</t>
+          <t>https://talk.naver.com/ct/w5wjfa</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,17 +1499,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>174</v>
+        <v>117</v>
       </c>
       <c r="Q11" t="n">
-        <v>262</v>
+        <v>348</v>
       </c>
       <c r="R11" t="n">
-        <v>436</v>
+        <v>465</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>37373427</t>
+          <t>1470902831</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37373427</t>
+          <t>https://m.place.naver.com/place/1470902831</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1698,10 +1698,10 @@
         <v>648</v>
       </c>
       <c r="Q13" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R13" t="n">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>

--- a/naver-place-crawler/results_health/의정부_헬스장.xlsx
+++ b/naver-place-crawler/results_health/의정부_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/incar50</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/spoany_62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -726,10 +726,10 @@
         <v>2042</v>
       </c>
       <c r="Q3" t="n">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="R3" t="n">
-        <v>4032</v>
+        <v>4029</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/athenagym</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2920</v>
+        <v>2924</v>
       </c>
       <c r="Q5" t="n">
         <v>969</v>
       </c>
       <c r="R5" t="n">
-        <v>3889</v>
+        <v>3893</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodyboom_ujb@naver.com</t>
+          <t>bodyboomone@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/bodyboomone</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1140,46 +1140,46 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>메이드라인 다이어트 의정부점</t>
+          <t>아이휘트니스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>madeline-@naver.com</t>
+          <t>kjm1184@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1304-3854</t>
+          <t>0507-1397-4568</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
+          <t>경기 의정부시 시민로 83 광장타워 9층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://made-line.co.kr</t>
+          <t>https://blog.naver.com/kjm1184</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1199,27 +1199,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4poji</t>
+          <t>https://talk.naver.com/ct/w4sloy</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>668</v>
+        <v>83</v>
       </c>
       <c r="Q8" t="n">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="R8" t="n">
-        <v>955</v>
+        <v>104</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,66 +1228,66 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1572526028</t>
+          <t>33811836</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572526028</t>
+          <t>https://m.place.naver.com/place/33811836</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>캥거루복싱GYM</t>
+          <t>메이드라인 다이어트 의정부점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>boxing6989@naver.com</t>
+          <t>madeline-@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>031-853-6989</t>
+          <t>0507-1304-3854</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 29 5층 501,502호</t>
+          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://made-line.co.kr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmk4z6o</t>
+          <t>https://talk.naver.com/ct/w4poji</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>174</v>
+        <v>668</v>
       </c>
       <c r="Q9" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="R9" t="n">
-        <v>436</v>
+        <v>955</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,47 +1326,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>37373427</t>
+          <t>1572526028</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37373427</t>
+          <t>https://m.place.naver.com/place/1572526028</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OPT트레이닝센터 다이어트 피지컬 1:1PT 금오점</t>
+          <t>캥거루복싱GYM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sunnydue@naver.com</t>
+          <t>boxing6989@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>031-853-6989</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 청사로 45 플래티넘1프라자 701호</t>
+          <t>경기 의정부시 오목로205번길 29 5층 501,502호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/kangaroo__boxinggym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1376,7 +1380,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45dto</t>
+          <t>https://talk.naver.com/ct/wmk4z6o</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>174</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>262</v>
       </c>
       <c r="R10" t="n">
-        <v>12</v>
+        <v>436</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1913501005</t>
+          <t>37373427</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1913501005</t>
+          <t>https://m.place.naver.com/place/37373427</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1442,29 +1446,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LT짐 PT</t>
+          <t>OPT트레이닝센터 다이어트 피지컬 1:1PT 금오점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ph5734@naver.com</t>
+          <t>sunnydue@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1397-5346</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 경의로 57 3층</t>
+          <t>경기 의정부시 청사로 45 플래티넘1프라자 701호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/opt087</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5wjfa</t>
+          <t>https://talk.naver.com/ct/w45dto</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,17 +1499,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>117</v>
+        <v>8</v>
       </c>
       <c r="Q11" t="n">
-        <v>348</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>465</v>
+        <v>12</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1470902831</t>
+          <t>1913501005</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1470902831</t>
+          <t>https://m.place.naver.com/place/1913501005</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://youtube.com/@한번더재활운동센터</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/gdrgs0753</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1720,7 +1720,105 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>필라테스 림 탑석역 점</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>pilateslim201@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1440-2832</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>경기 의정부시 오목로 33 2층 201호</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pilateslim201/224254625203</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wjnmgc7</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>712</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1093</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1805</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1347002622</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1347002622</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/의정부_헬스장.xlsx
+++ b/naver-place-crawler/results_health/의정부_헬스장.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="25" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -586,7 +586,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/incar50</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/spoany_62</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/allin_gym1?igsh=Yzk1bGZicTR1dmEw&amp;utm_source=qr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/athenagym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://youtube.com/watch?v=Xw10EOdN3w8</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1020,10 +1020,10 @@
         <v>154</v>
       </c>
       <c r="Q6" t="n">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="R6" t="n">
-        <v>804</v>
+        <v>810</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>bodyboomone@naver.com</t>
+          <t>bodyboom_ujb@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/bodyboomone</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1147,39 +1147,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>아이휘트니스</t>
+          <t>메이드라인 다이어트 의정부점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>kjm1184@naver.com</t>
+          <t>made-line@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1397-4568</t>
+          <t>0507-1304-3854</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 의정부시 시민로 83 광장타워 9층</t>
+          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kjm1184</t>
+          <t>https://made-line.co.kr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1199,27 +1199,27 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4sloy</t>
+          <t>https://talk.naver.com/ct/w4poji</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>83</v>
+        <v>668</v>
       </c>
       <c r="Q8" t="n">
-        <v>21</v>
+        <v>287</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>955</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>33811836</t>
+          <t>1572526028</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/33811836</t>
+          <t>https://m.place.naver.com/place/1572526028</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,49 +1245,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>메이드라인 다이어트 의정부점</t>
+          <t>캥거루복싱GYM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>madeline-@naver.com</t>
+          <t>boxing6989@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1304-3854</t>
+          <t>031-853-6989</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 의정부시 가능로 105 성원빌딩 4층</t>
+          <t>경기 의정부시 오목로205번길 29 5층 501,502호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://made-line.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4poji</t>
+          <t>https://talk.naver.com/ct/wmk4z6o</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>668</v>
+        <v>174</v>
       </c>
       <c r="Q9" t="n">
-        <v>287</v>
+        <v>262</v>
       </c>
       <c r="R9" t="n">
-        <v>955</v>
+        <v>436</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1572526028</t>
+          <t>37373427</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1572526028</t>
+          <t>https://m.place.naver.com/place/37373427</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1343,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>캥거루복싱GYM</t>
+          <t>한번더재활운동센터</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>boxing6989@naver.com</t>
+          <t>kongja21@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>031-853-6989</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 의정부시 오목로205번길 29 5층 501,502호</t>
+          <t>경기 의정부시 세석로 20 2층 204호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/kangaroo__boxinggym</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1380,7 +1376,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1395,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wmk4z6o</t>
+          <t>https://talk.naver.com/ct/weppdix</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,17 +1401,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>174</v>
+        <v>65</v>
       </c>
       <c r="Q10" t="n">
-        <v>262</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>436</v>
+        <v>67</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>37373427</t>
+          <t>2072368822</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37373427</t>
+          <t>https://m.place.naver.com/place/2072368822</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,30 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>실내골프연습장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OPT트레이닝센터 다이어트 피지컬 1:1PT 금오점</t>
+          <t>GDR골프아카데미 고산지구점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sunnydue@naver.com</t>
+          <t>gdrgs0753@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1471-0754</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 의정부시 청사로 45 플래티넘1프라자 701호</t>
+          <t>경기 의정부시 월유로 16 GS프라자 9층 903호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/opt087</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w45dto</t>
+          <t>https://talk.naver.com/ct/w4539d</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>8</v>
+        <v>648</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>461</v>
       </c>
       <c r="R11" t="n">
-        <v>12</v>
+        <v>1109</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1913501005</t>
+          <t>1057272528</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1913501005</t>
+          <t>https://m.place.naver.com/place/1057272528</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1535,30 +1535,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한번더재활운동센터</t>
+          <t>필라테스 림 탑석역 점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>kongja21@naver.com</t>
+          <t>pilateslim201@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1440-2832</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 의정부시 세석로 20 2층 204호</t>
+          <t>경기 의정부시 오목로 33 2층 201호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://youtube.com/@한번더재활운동센터</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1568,7 +1572,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1583,27 +1587,27 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/weppdix</t>
+          <t>https://talk.naver.com/ct/wjnmgc7</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>65</v>
+        <v>712</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>1093</v>
       </c>
       <c r="R12" t="n">
-        <v>67</v>
+        <v>1805</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,211 +1616,15 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2072368822</t>
+          <t>1347002622</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2072368822</t>
+          <t>https://m.place.naver.com/place/1347002622</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>실내골프연습장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GDR골프아카데미 고산지구점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>gdrgs0753@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1471-0754</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기 의정부시 월유로 16 GS프라자 9층 903호</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/gdrgs0753</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4539d</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>648</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>461</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1109</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1057272528</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1057272528</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>필라테스</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>필라테스 림 탑석역 점</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>pilateslim201@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1440-2832</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기 의정부시 오목로 33 2층 201호</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/pilateslim201/224254625203</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wjnmgc7</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>712</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1093</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1805</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1347002622</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1347002622</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
